--- a/public/files/cases-onecall.xlsx
+++ b/public/files/cases-onecall.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Навык: Держать высокий FCR стабильно. Дедлайн: пятница, 15:00 МСК.</t>
+          <t>Навык: Держать высокий FCR стабильно. Дедлайн: пятница, 13:00 МСК.</t>
         </is>
       </c>
     </row>

--- a/public/files/cases-onecall.xlsx
+++ b/public/files/cases-onecall.xlsx
@@ -491,7 +491,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Обсудите кейсы командой, впишите общий ответ в колонку «Ваш ответ» и загрузите файл обратно в личный кабинет.</t>
+          <t>Во всех кейсах клиент — сегмент «Масс». Решайте так, независимо от вашего направления. Обсудите кейсы командой, впишите общий ответ в колонку «Ваш ответ» и загрузите файл обратно в личный кабинет.</t>
         </is>
       </c>
     </row>
